--- a/TRICKS_LEGENDARY.xlsx
+++ b/TRICKS_LEGENDARY.xlsx
@@ -1494,7 +1494,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Build: 2026-10-21 · r622 · The common Trick sheet rebuilt on an audit of the current code</t>
+          <t>Build: 2026-10-21 · r624 · The owner's rare Trick pass: numbers, six custom improvement ladders, Heron, Resonance, Kaleidoscope, Woodpecker, Crossroads, Perfect Ten, chance counts on chips, unplayable-hand Tricks offered less</t>
         </is>
       </c>
     </row>

--- a/TRICKS_LEGENDARY.xlsx
+++ b/TRICKS_LEGENDARY.xlsx
@@ -1494,7 +1494,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Build: 2026-10-21 · r624 · The owner's rare Trick pass: numbers, six custom improvement ladders, Heron, Resonance, Kaleidoscope, Woodpecker, Crossroads, Perfect Ten, chance counts on chips, unplayable-hand Tricks offered less</t>
+          <t>Build: 2026-10-21 · r625 · The owner's epic Trick pass: numbers, 24 custom improvement ladders with hooks, Temporal Rift force-triggers, Move as One / Rain Check / Wait For Iiiit are Knacks</t>
         </is>
       </c>
     </row>
